--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$I$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$I$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2455,28 +2455,28 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>979</v>
+        <v>100</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/7552480392.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2486,36 +2486,67 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>12979</v>
+        <v>979</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-0/7552480392.jpg</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>jf011e</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>12979</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I66"/>
+  <autoFilter ref="A1:I67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-x/7552494033.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/7564782452.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_3.png</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-3/7397476995.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-b/7394683367.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-f/7562267475.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7552515129.jpg|https://ir.ozone.ru/s3/multimedia-1-e/7562267474.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -740,7 +740,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-6/7438257402.jpg|https://ir.ozone.ru/s3/multimedia-1-j/7940622691.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/7552527268.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_7.png</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/10284642862.jpg|https://ir.ozone.ru/s3/multimedia-1-s/10284643468.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/10266231352.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7514787118.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_4.png</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/9080058296.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_5.png</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-d/11439945697.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-d/10272235369.jpg|https://ir.ozone.ru/s3/multimedia-1-i/7562188674.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7562188673.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/10218932732.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/10218920828.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/9097867580.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-3/7393195947.jpg|https://ir.ozone.ru/s3/multimedia-1-8/7940348396.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-s/7474295980.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7552748443.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-x/10202430057.jpg|https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-b/10217896103.jpg|https://ir.ozone.ru/s3/multimedia-1-u/10217896230.jpg|https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563834782.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_2.png</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-i/10218060954.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7438299761.jpg|https://ir.ozone.ru/s3/multimedia-1-q/7940643686.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-9/7397393229.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940536823.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/7474196593.jpg|https://ir.ozone.ru/s3/multimedia-1-q/9122060114.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_6.png</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg|https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg|https://ir.ozone.ru/s3/multimedia-1-a/10218089134.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7394696306.jpg|https://ir.ozone.ru/s3/multimedia-1-w/7940435756.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7394694007.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940483111.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7940483230.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940483037.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.png</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563422546.jpg|https://ir.ozone.ru/s3/multimedia-1-a/7562264806.jpg|https://ir.ozone.ru/s3/multimedia-1-6/7559282022.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7559347497.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.png</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-l/7663847097.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-7/7474290559.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940614484.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-6/10266207810.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7562154593.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-e/7394678726.jpg|https://ir.ozone.ru/s3/multimedia-1-7/7940398579.jpg|https://ir.ozone.ru/s3/multimedia-1-d/7940398873.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940398988.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_7.png</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-s/8564480416.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_5.png</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/7625662237.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/8529517784.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/8527504576.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/8550952630.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-g/8550871144.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-9/7564972365.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-o/8550458916.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-m/8550569326.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7515410251.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-5/9097856825.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_6.png</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-e/8527590482.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-n/8527642655.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/7552480392.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -926,7 +926,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_5.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7663845476.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_7.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_6.png</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_6.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_6.png</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-x/7552494033.jpg</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-w/7564782452.jpg</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-3/7397476995.jpg</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-b/7394683367.jpg</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-f/7562267475.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7552515129.jpg|https://ir.ozone.ru/s3/multimedia-1-e/7562267474.jpg</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -740,7 +740,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-6/7438257402.jpg|https://ir.ozone.ru/s3/multimedia-1-j/7940622691.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_7.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-4/7552527268.jpg</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-y/10284642862.jpg|https://ir.ozone.ru/s3/multimedia-1-s/10284643468.jpg</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-4/10266231352.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7514787118.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/9080058296.jpg</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-d/11439945697.jpg</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-d/10272235369.jpg|https://ir.ozone.ru/s3/multimedia-1-i/7562188674.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7562188673.jpg</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/10218932732.jpg</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-w/10218920828.jpg</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-w/9097867580.jpg</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-3/7393195947.jpg|https://ir.ozone.ru/s3/multimedia-1-8/7940348396.jpg</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-s/7474295980.jpg</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/7552748443.jpg</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-x/10202430057.jpg|https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-b/10217896103.jpg|https://ir.ozone.ru/s3/multimedia-1-u/10217896230.jpg|https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563834782.jpg</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-i/10218060954.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7438299761.jpg|https://ir.ozone.ru/s3/multimedia-1-q/7940643686.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-9/7397393229.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940536823.jpg</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_6.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-1/7474196593.jpg|https://ir.ozone.ru/s3/multimedia-1-q/9122060114.jpg</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg|https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg|https://ir.ozone.ru/s3/multimedia-1-a/10218089134.jpg</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/7394696306.jpg|https://ir.ozone.ru/s3/multimedia-1-w/7940435756.jpg</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/7394694007.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940483111.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7940483230.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940483037.jpg</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563422546.jpg|https://ir.ozone.ru/s3/multimedia-1-a/7562264806.jpg|https://ir.ozone.ru/s3/multimedia-1-6/7559282022.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7559347497.jpg</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-l/7663847097.jpg</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/7663845476.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-7/7474290559.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940614484.jpg</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-6/10266207810.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7562154593.jpg</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_6.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-e/7394678726.jpg|https://ir.ozone.ru/s3/multimedia-1-7/7940398579.jpg|https://ir.ozone.ru/s3/multimedia-1-d/7940398873.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940398988.jpg</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_5.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-s/8564480416.jpg</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-1/7625662237.jpg</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/8529517784.jpg</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-4/8527504576.jpg</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-y/8550952630.jpg</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-g/8550871144.jpg</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-9/7564972365.jpg</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-o/8550458916.jpg</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-m/8550569326.jpg</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/7515410251.jpg</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_6.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-5/9097856825.jpg</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-e/8527590482.jpg</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-n/8527642655.jpg</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-0/7552480392.jpg</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-x/7552494033.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/7564782452.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_3.png</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-3/7397476995.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-b/7394683367.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-f/7562267475.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7552515129.jpg|https://ir.ozone.ru/s3/multimedia-1-e/7562267474.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -740,7 +740,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-6/7438257402.jpg|https://ir.ozone.ru/s3/multimedia-1-j/7940622691.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/7552527268.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_7.png</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/10284642862.jpg|https://ir.ozone.ru/s3/multimedia-1-s/10284643468.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/10266231352.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7514787118.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/9080058296.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-d/11439945697.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-d/10272235369.jpg|https://ir.ozone.ru/s3/multimedia-1-i/7562188674.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7562188673.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/10218932732.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/10218920828.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/9097867580.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-3/7393195947.jpg|https://ir.ozone.ru/s3/multimedia-1-8/7940348396.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-s/7474295980.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7552748443.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-x/10202430057.jpg|https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-b/10217896103.jpg|https://ir.ozone.ru/s3/multimedia-1-u/10217896230.jpg|https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563834782.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_2.png</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-i/10218060954.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7438299761.jpg|https://ir.ozone.ru/s3/multimedia-1-q/7940643686.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-9/7397393229.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940536823.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/7474196593.jpg|https://ir.ozone.ru/s3/multimedia-1-q/9122060114.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_6.png</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg|https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg|https://ir.ozone.ru/s3/multimedia-1-a/10218089134.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7394696306.jpg|https://ir.ozone.ru/s3/multimedia-1-w/7940435756.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7394694007.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940483111.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7940483230.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940483037.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.png</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563422546.jpg|https://ir.ozone.ru/s3/multimedia-1-a/7562264806.jpg|https://ir.ozone.ru/s3/multimedia-1-6/7559282022.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7559347497.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.png</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-l/7663847097.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7663845476.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-7/7474290559.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940614484.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-6/10266207810.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7562154593.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-e/7394678726.jpg|https://ir.ozone.ru/s3/multimedia-1-7/7940398579.jpg|https://ir.ozone.ru/s3/multimedia-1-d/7940398873.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940398988.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_6.png</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-s/8564480416.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_5.png</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/7625662237.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/8529517784.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/8527504576.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-g/8550871144.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-9/7564972365.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-o/8550458916.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-m/8550569326.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7515410251.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-5/9097856825.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_6.png</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-e/8527590482.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-n/8527642655.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/7552480392.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/8550952630.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_6.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_4.png</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +499,11 @@
           <t>Заметки</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Код ТН ВЭД (пусто = не менять; заполните, если Ozon пишет 'не заполнен обязательный атрибут ТН ВЭД')</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -523,12 +529,13 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-x/7552494033.jpg</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -554,12 +561,13 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-w/7564782452.jpg</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -591,6 +599,7 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -616,12 +625,13 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-3/7397476995.jpg</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -653,6 +663,7 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -678,12 +689,13 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-b/7394683367.jpg</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -709,12 +721,13 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-f/7562267475.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7552515129.jpg|https://ir.ozone.ru/s3/multimedia-1-e/7562267474.jpg</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -740,12 +753,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-6/7438257402.jpg|https://ir.ozone.ru/s3/multimedia-1-j/7940622691.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -771,12 +789,13 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_7.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-4/7552527268.jpg</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -802,12 +821,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-y/10284642862.jpg|https://ir.ozone.ru/s3/multimedia-1-s/10284643468.jpg</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -833,12 +857,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-4/10266231352.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7514787118.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -864,12 +893,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -901,6 +935,7 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -926,12 +961,13 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/9080058296.jpg</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -957,12 +993,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-d/11439945697.jpg</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -988,12 +1029,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-d/10272235369.jpg|https://ir.ozone.ru/s3/multimedia-1-i/7562188674.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7562188673.jpg</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1019,12 +1065,13 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/10218932732.jpg</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1050,12 +1097,13 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-w/10218920828.jpg</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1081,12 +1129,13 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-w/9097867580.jpg</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1112,12 +1161,13 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-3/7393195947.jpg|https://ir.ozone.ru/s3/multimedia-1-8/7940348396.jpg</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1143,12 +1193,13 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-s/7474295980.jpg</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1174,12 +1225,13 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/7552748443.jpg</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1211,6 +1263,11 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1236,12 +1293,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-x/10202430057.jpg|https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-b/10217896103.jpg|https://ir.ozone.ru/s3/multimedia-1-u/10217896230.jpg|https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1267,12 +1329,13 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563834782.jpg</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1298,12 +1361,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-i/10218060954.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7438299761.jpg|https://ir.ozone.ru/s3/multimedia-1-q/7940643686.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>8708409109 - Коробки передач и их части штампов.из стали, прочие</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1329,12 +1397,13 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-9/7397393229.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940536823.jpg</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1360,12 +1429,13 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_6.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-1/7474196593.jpg|https://ir.ozone.ru/s3/multimedia-1-q/9122060114.jpg</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1391,12 +1461,17 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg|https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg|https://ir.ozone.ru/s3/multimedia-1-a/10218089134.jpg</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1422,12 +1497,13 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/7394696306.jpg|https://ir.ozone.ru/s3/multimedia-1-w/7940435756.jpg</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1453,12 +1529,13 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/7394694007.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940483111.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7940483230.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940483037.jpg</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1490,6 +1567,7 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1515,12 +1593,13 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563422546.jpg|https://ir.ozone.ru/s3/multimedia-1-a/7562264806.jpg|https://ir.ozone.ru/s3/multimedia-1-6/7559282022.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7559347497.jpg</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1552,6 +1631,7 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1577,12 +1657,13 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-l/7663847097.jpg</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1614,6 +1695,7 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1639,12 +1721,13 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/7663845476.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1670,12 +1753,13 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-7/7474290559.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940614484.jpg</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1701,12 +1785,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-6/10266207810.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7562154593.jpg</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1738,6 +1827,7 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1763,12 +1853,13 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_6.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-e/7394678726.jpg|https://ir.ozone.ru/s3/multimedia-1-7/7940398579.jpg|https://ir.ozone.ru/s3/multimedia-1-d/7940398873.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940398988.jpg</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="3" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1794,12 +1885,13 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1825,12 +1917,13 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1856,12 +1949,13 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_5.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-s/8564480416.jpg</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1887,12 +1981,13 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-1/7625662237.jpg</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1924,6 +2019,7 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="3" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1949,12 +2045,13 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/8529517784.jpg</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="3" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1986,6 +2083,7 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2011,12 +2109,13 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-4/8527504576.jpg</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="3" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2042,12 +2141,13 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-y/8550952630.jpg</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="3" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2079,6 +2179,7 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2104,12 +2205,13 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-g/8550871144.jpg</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2135,12 +2237,13 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-9/7564972365.jpg</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2172,6 +2275,11 @@
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2197,12 +2305,13 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-o/8550458916.jpg</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2228,12 +2337,13 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-m/8550569326.jpg</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2259,12 +2369,13 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/7515410251.jpg</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2290,12 +2401,13 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-5/9097856825.jpg</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2327,6 +2439,7 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2358,6 +2471,7 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2383,12 +2497,13 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-e/8527590482.jpg</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2420,6 +2535,11 @@
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2445,12 +2565,13 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-n/8527642655.jpg</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="3" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2482,6 +2603,11 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>8421230000 - Оборудование и устройства для фильтрования масла или топлива в двигателях внутреннего сгорания</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2507,12 +2633,13 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-0/7552480392.jpg</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2544,9 +2671,10 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I67"/>
+  <autoFilter ref="A1:J67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-x/7552494033.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/7564782452.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_3.png</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-3/7397476995.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-b/7394683367.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-f/7562267475.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7552515129.jpg|https://ir.ozone.ru/s3/multimedia-1-e/7562267474.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-6/7438257402.jpg|https://ir.ozone.ru/s3/multimedia-1-j/7940622691.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/7552527268.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_7.png</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/10284642862.jpg|https://ir.ozone.ru/s3/multimedia-1-s/10284643468.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/10266231352.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7514787118.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/9080058296.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-d/11439945697.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-d/10272235369.jpg|https://ir.ozone.ru/s3/multimedia-1-i/7562188674.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7562188673.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/10218932732.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/10218920828.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/9097867580.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-3/7393195947.jpg|https://ir.ozone.ru/s3/multimedia-1-8/7940348396.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-s/7474295980.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7552748443.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-x/10202430057.jpg|https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-b/10217896103.jpg|https://ir.ozone.ru/s3/multimedia-1-u/10217896230.jpg|https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563834782.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_2.png</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-i/10218060954.jpg|https://ir.ozone.ru/s3/multimedia-1-h/7940622941.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940606805.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7438299761.jpg|https://ir.ozone.ru/s3/multimedia-1-q/7940643686.jpg|https://ir.ozone.ru/s3/multimedia-1-l/7940606601.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-9/7397393229.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940536823.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/7474196593.jpg|https://ir.ozone.ru/s3/multimedia-1-q/9122060114.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_6.png</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg|https://ir.ozone.ru/s3/multimedia-1-q/10218089294.jpg|https://ir.ozone.ru/s3/multimedia-1-a/10218089134.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7394696306.jpg|https://ir.ozone.ru/s3/multimedia-1-w/7940435756.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7394694007.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7940483111.jpg|https://ir.ozone.ru/s3/multimedia-1-m/7940483230.jpg|https://ir.ozone.ru/s3/multimedia-1-9/7940483037.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.png</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563422546.jpg|https://ir.ozone.ru/s3/multimedia-1-a/7562264806.jpg|https://ir.ozone.ru/s3/multimedia-1-6/7559282022.jpg|https://ir.ozone.ru/s3/multimedia-1-x/7559347497.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.png</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-l/7663847097.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7663845476.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-7/7474290559.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940614484.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-6/10266207810.jpg|https://ir.ozone.ru/s3/multimedia-1-t/7562154593.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-e/7394678726.jpg|https://ir.ozone.ru/s3/multimedia-1-7/7940398579.jpg|https://ir.ozone.ru/s3/multimedia-1-d/7940398873.jpg|https://ir.ozone.ru/s3/multimedia-1-k/7940398988.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_6.png</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/7425960104.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-s/8564480416.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_5.png</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/7625662237.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/8529517784.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/8527504576.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/8550952630.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-g/8550871144.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-9/7564972365.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-o/8550458916.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-m/8550569326.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/7515410251.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-5/9097856825.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-e/8527590482.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-n/8527642655.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/7552480392.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$J$67</definedName>
@@ -535,7 +535,11 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -567,7 +571,11 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -599,7 +607,11 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -631,7 +643,11 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -663,7 +679,11 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -695,7 +715,11 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -727,7 +751,11 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -761,7 +789,7 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -795,7 +823,11 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -829,7 +861,7 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -865,7 +897,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -901,7 +933,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -935,7 +967,11 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -967,7 +1003,11 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1001,7 +1041,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1077,7 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1111,11 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1103,7 +1147,11 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1135,7 +1183,11 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1167,7 +1219,11 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1199,7 +1255,11 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1231,7 +1291,11 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1265,7 +1329,7 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1365,7 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1399,11 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1369,7 +1437,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8708409109 - Коробки передач и их части штампов.из стали, прочие</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1471,11 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1435,7 +1507,11 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1469,7 +1545,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1579,11 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1535,7 +1615,11 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1567,7 +1651,11 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1599,7 +1687,11 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1631,7 +1723,11 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1663,7 +1759,11 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1695,7 +1795,11 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1727,7 +1831,11 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1759,7 +1867,11 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1793,7 +1905,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1939,11 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1859,7 +1975,11 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="3" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1891,7 +2011,11 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1923,7 +2047,11 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1955,7 +2083,11 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1987,7 +2119,11 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2019,7 +2155,11 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="3" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2051,7 +2191,11 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="3" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2083,7 +2227,11 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2115,7 +2263,11 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="3" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2147,7 +2299,11 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="3" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2179,7 +2335,11 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2211,7 +2371,11 @@
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2243,7 +2407,11 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2277,7 +2445,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2479,11 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2343,7 +2515,11 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2375,7 +2551,11 @@
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>8708999709</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2407,7 +2587,11 @@
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2439,7 +2623,11 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2471,7 +2659,11 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2503,7 +2695,11 @@
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2537,7 +2733,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2767,11 @@
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="3" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2639,7 +2839,11 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2671,7 +2875,11 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J67"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$J$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$J$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>8708999709</t>
+          <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
     </row>
@@ -2589,71 +2589,67 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>DQ500-a</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
+          <t>Набор корпус фильтра + фильтр DSG7 DQ500 0BH</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>979</v>
+        <v>5879</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-1/14848098301.jpg|https://ir.ozone.ru/s3/multimedia-1-p/14848103293.jpg</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>8708409909</t>
-        </is>
-      </c>
+      <c r="J60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
+          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;</t>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>8890</v>
+        <v>979</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12000</v>
+        <v>1500</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2661,35 +2657,35 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра EA888</t>
+          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>4741</v>
+        <v>8890</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2697,71 +2693,67 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>EA888 Gen.3 магнит + корпус алюминиевый комплект</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>6690</v>
+        <v>3879</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>8708409909</t>
-        </is>
-      </c>
+      <c r="J63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
+          <t>Корпус фильтра EA888</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2366</v>
+        <v>4741</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2769,35 +2761,35 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>EA888 Gen.3 магнит + корпус алюминиевый комплект</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>100</v>
+        <v>6690</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2805,35 +2797,35 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>8421230000 - Оборудование и устройства для фильтрования масла или топлива в двигателях внутреннего сгорания</t>
+          <t>8708409909</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>979</v>
+        <v>2366</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2841,35 +2833,35 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>12979</v>
+        <v>100</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-p/14845895953.jpg</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -2877,12 +2869,84 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8421230000 - Оборудование и устройства для фильтрования масла или топлива в двигателях внутреннего сгорания</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>WHT001922</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>jf011e</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>12979</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J67"/>
+  <autoFilter ref="A1:J69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -2861,7 +2861,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-p/14845895953.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-t/14848101785.jpg</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-f/14848104075.jpg|https://ir.ozone.ru/s3/multimedia-1-2/14848099634.jpg|https://ir.ozone.ru/s3/multimedia-1-2/14848107986.jpg</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-h/14848107497.jpg|https://ir.ozone.ru/s3/multimedia-1-w/14848101392.jpg|https://ir.ozone.ru/s3/multimedia-1-1/14848097509.jpg|https://ir.ozone.ru/s3/multimedia-1-c/14848097268.jpg</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-n/14848104479.jpg|https://ir.ozone.ru/s3/multimedia-1-q/14848106426.jpg|https://ir.ozone.ru/s3/multimedia-1-k/14848101956.jpg</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -781,7 +781,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-i/14848109406.jpg|https://ir.ozone.ru/s3/multimedia-1-q/14848097714.jpg</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -789,7 +789,7 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_7.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-t/14848102901.jpg|https://ir.ozone.ru/s3/multimedia-1-u/14848098798.jpg|https://ir.ozone.ru/s3/multimedia-1-s/14848100848.jpg|https://ir.ozone.ru/s3/multimedia-1-r/14848103799.jpg|https://ir.ozone.ru/s3/multimedia-1-n/14848106243.jpg|https://ir.ozone.ru/s3/multimedia-1-r/14848108227.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14848102908.jpg</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-u/14848104306.jpg|https://ir.ozone.ru/s3/multimedia-1-c/14848096872.jpg</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -861,7 +861,7 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-n/14848102643.jpg|https://ir.ozone.ru/s3/multimedia-1-5/14848102625.jpg|https://ir.ozone.ru/s3/multimedia-1-2/14848101758.jpg</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -897,7 +897,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-f/14848096587.jpg|https://ir.ozone.ru/s3/multimedia-1-t/14848103945.jpg</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -933,7 +933,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-i/14848104834.jpg</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-2/14848098842.jpg|https://ir.ozone.ru/s3/multimedia-1-b/14848107419.jpg</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1077,14 +1077,14 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1094,18 +1094,18 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7979</v>
+        <v>3879</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-tmp-6/item-pic-2a3c594b7813848476bc066f768e0f1d.jpg|https://ir.ozone.ru/s3/multimedia-tmp-3/item-pic-16e5a96e917465720f68d39bec57e767.jpg</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1120,17 +1120,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1156,28 +1156,28 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3879</v>
+        <v>7979</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-e/14848103966.jpg|https://ir.ozone.ru/s3/multimedia-1-p/14848102465.jpg</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-f/14848104147.jpg|https://ir.ozone.ru/s3/multimedia-1-4/14848097836.jpg</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-a/14848106446.jpg|https://ir.ozone.ru/s3/multimedia-1-6/14848110726.jpg</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-0/14848099812.jpg|https://ir.ozone.ru/s3/multimedia-1-v/14848099087.jpg|https://ir.ozone.ru/s3/multimedia-1-g/14848107676.jpg</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM 0CW</t>
+          <t>Мехатроник DSG7 подходит на ВСЕ DQ200 0am 0cw</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/14848100563.jpg|https://ir.ozone.ru/s3/multimedia-1-6/14848109286.jpg</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1365,7 +1365,7 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-j/14848102747.jpg|https://ir.ozone.ru/s3/multimedia-1-b/14848100435.jpg</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409109 - Коробки передач и их части штампов.из стали, прочие</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-3/14848098879.jpg</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-2/14848097078.jpg|https://ir.ozone.ru/s3/multimedia-1-d/14848104973.jpg</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/14851642351.jpg|https://ir.ozone.ru/s3/multimedia-1-j/14848102423.jpg</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-d/14848107925.jpg</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-i/14851639530.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/14848102934.jpg</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-p/14848105129.jpg</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1905,7 +1905,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-4/14851638904.jpg|https://ir.ozone.ru/s3/multimedia-1-i/14848100838.jpg</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-q/14851647350.jpg|https://ir.ozone.ru/s3/multimedia-1-5/14848106945.jpg</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_5.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-4/14848097080.jpg|https://ir.ozone.ru/s3/multimedia-1-p/14848103113.jpg|https://ir.ozone.ru/s3/multimedia-1-8/14848100684.jpg|https://ir.ozone.ru/s3/multimedia-1-r/14848098543.jpg|https://ir.ozone.ru/s3/multimedia-1-a/14848107490.jpg</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-7/14848107271.jpg|https://ir.ozone.ru/s3/multimedia-1-x/14848101393.jpg</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-y/14848102582.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14848097292.jpg</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-y/14848105642.jpg|https://ir.ozone.ru/s3/multimedia-1-h/14848101233.jpg|https://ir.ozone.ru/s3/multimedia-1-1/14848106905.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14848103664.jpg</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-k/14848105268.jpg|https://ir.ozone.ru/s3/multimedia-1-i/14848106094.jpg|https://ir.ozone.ru/s3/multimedia-1-2/14848101830.jpg|https://ir.ozone.ru/s3/multimedia-1-k/14848105736.jpg|https://ir.ozone.ru/s3/multimedia-1-a/14848101514.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14848106760.jpg|https://ir.ozone.ru/s3/multimedia-1-q/14848098398.jpg</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-a/14848106518.jpg</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-p/14848105993.jpg|https://ir.ozone.ru/s3/multimedia-1-o/14848101816.jpg</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-v/14848100779.jpg|https://ir.ozone.ru/s3/multimedia-1-o/14848098540.jpg|https://ir.ozone.ru/s3/multimedia-1-u/14848107438.jpg</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-r/14848102827.jpg</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-s/14848100416.jpg</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-p/14848103293.jpg|https://ir.ozone.ru/s3/multimedia-1-c/14848113972.jpg</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2596,60 +2596,64 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>DQ500-a</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DSG7 DQ500 0BH</t>
+          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла</t>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>5879</v>
+        <v>979</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/14848098301.jpg|https://ir.ozone.ru/s3/multimedia-1-p/14848103293.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
+          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>979</v>
+        <v>8890</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1500</v>
+        <v>12000</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2664,28 +2668,28 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>8890</v>
+        <v>3879</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-9/14860646217.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14860646604.jpg|https://ir.ozone.ru/s3/multimedia-1-b/14860761059.jpg</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2693,67 +2697,71 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра EA888</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>3879</v>
+        <v>4741</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>6000</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-0/14848107048.jpg</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра EA888</t>
+          <t>EA888 Gen.3 магнит + корпус алюминиевый комплект</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>4741</v>
+        <v>6690</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2761,35 +2769,35 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>EA888 Gen.3 магнит + корпус алюминиевый комплект</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>6690</v>
+        <v>2366</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-i/14848102062.jpg|https://ir.ozone.ru/s3/multimedia-1-h/14848105733.jpg</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2797,35 +2805,35 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
+          <t>Тестовый товар не публикуется</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>2366</v>
+        <v>100</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-p/14845895953.jpg</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2833,35 +2841,35 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8421230000 - Оборудование и устройства для фильтрования масла или топлива в двигателях внутреннего сгорания</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>100</v>
+        <v>979</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-1/14848101361.jpg</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -2869,35 +2877,35 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>8421230000 - Оборудование и устройства для фильтрования масла или топлива в двигателях внутреннего сгорания</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>979</v>
+        <v>12979</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1500</v>
+        <v>15000</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+          <t>https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -2912,36 +2920,28 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
-        </is>
-      </c>
+          <t>Накладка на автомобиль на педали, 3 шт.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>12979</v>
+        <v>950</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
-        </is>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
     </row>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-t/14848101785.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-f/14848104075.jpg|https://ir.ozone.ru/s3/multimedia-1-2/14848099634.jpg|https://ir.ozone.ru/s3/multimedia-1-2/14848107986.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_3.png</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-h/14848107497.jpg|https://ir.ozone.ru/s3/multimedia-1-w/14848101392.jpg|https://ir.ozone.ru/s3/multimedia-1-1/14848097509.jpg|https://ir.ozone.ru/s3/multimedia-1-c/14848097268.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-n/14848104479.jpg|https://ir.ozone.ru/s3/multimedia-1-q/14848106426.jpg|https://ir.ozone.ru/s3/multimedia-1-k/14848101956.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -781,7 +781,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-i/14848109406.jpg|https://ir.ozone.ru/s3/multimedia-1-q/14848097714.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-t/14848102901.jpg|https://ir.ozone.ru/s3/multimedia-1-u/14848098798.jpg|https://ir.ozone.ru/s3/multimedia-1-s/14848100848.jpg|https://ir.ozone.ru/s3/multimedia-1-r/14848103799.jpg|https://ir.ozone.ru/s3/multimedia-1-n/14848106243.jpg|https://ir.ozone.ru/s3/multimedia-1-r/14848108227.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14848102908.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_7.png</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-u/14848104306.jpg|https://ir.ozone.ru/s3/multimedia-1-c/14848096872.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -889,7 +889,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-n/14848102643.jpg|https://ir.ozone.ru/s3/multimedia-1-5/14848102625.jpg|https://ir.ozone.ru/s3/multimedia-1-2/14848101758.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-f/14848096587.jpg|https://ir.ozone.ru/s3/multimedia-1-t/14848103945.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-i/14848104834.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-2/14848098842.jpg|https://ir.ozone.ru/s3/multimedia-1-b/14848107419.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-e/14848103966.jpg|https://ir.ozone.ru/s3/multimedia-1-p/14848102465.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-f/14848104147.jpg|https://ir.ozone.ru/s3/multimedia-1-4/14848097836.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-a/14848106446.jpg|https://ir.ozone.ru/s3/multimedia-1-6/14848110726.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/14848099812.jpg|https://ir.ozone.ru/s3/multimedia-1-v/14848099087.jpg|https://ir.ozone.ru/s3/multimedia-1-g/14848107676.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/14848100563.jpg|https://ir.ozone.ru/s3/multimedia-1-6/14848109286.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-j/14848102747.jpg|https://ir.ozone.ru/s3/multimedia-1-b/14848100435.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-3/14848098879.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-2/14848097078.jpg|https://ir.ozone.ru/s3/multimedia-1-d/14848104973.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/14851642351.jpg|https://ir.ozone.ru/s3/multimedia-1-j/14848102423.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-d/14848107925.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-i/14851639530.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/14848102934.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-p/14848105129.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/14851638904.jpg|https://ir.ozone.ru/s3/multimedia-1-i/14848100838.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/14851647350.jpg|https://ir.ozone.ru/s3/multimedia-1-5/14848106945.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-4/14848097080.jpg|https://ir.ozone.ru/s3/multimedia-1-p/14848103113.jpg|https://ir.ozone.ru/s3/multimedia-1-8/14848100684.jpg|https://ir.ozone.ru/s3/multimedia-1-r/14848098543.jpg|https://ir.ozone.ru/s3/multimedia-1-a/14848107490.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_5.png</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-7/14848107271.jpg|https://ir.ozone.ru/s3/multimedia-1-x/14848101393.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/14848102582.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14848097292.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/14848105642.jpg|https://ir.ozone.ru/s3/multimedia-1-h/14848101233.jpg|https://ir.ozone.ru/s3/multimedia-1-1/14848106905.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14848103664.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-k/14848105268.jpg|https://ir.ozone.ru/s3/multimedia-1-i/14848106094.jpg|https://ir.ozone.ru/s3/multimedia-1-2/14848101830.jpg|https://ir.ozone.ru/s3/multimedia-1-k/14848105736.jpg|https://ir.ozone.ru/s3/multimedia-1-a/14848101514.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14848106760.jpg|https://ir.ozone.ru/s3/multimedia-1-q/14848098398.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-a/14848106518.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-p/14848105993.jpg|https://ir.ozone.ru/s3/multimedia-1-o/14848101816.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-v/14848100779.jpg|https://ir.ozone.ru/s3/multimedia-1-o/14848098540.jpg|https://ir.ozone.ru/s3/multimedia-1-u/14848107438.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-r/14848102827.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-s/14848100416.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-p/14848103293.jpg|https://ir.ozone.ru/s3/multimedia-1-c/14848113972.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-0/14848107048.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-i/14848102062.jpg|https://ir.ozone.ru/s3/multimedia-1-h/14848105733.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-p/14845895953.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/14848101361.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -2935,7 +2935,11 @@
       <c r="E69" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="F69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.png</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$J$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$K$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,7 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,6 +505,11 @@
           <t>Код ТН ВЭД (пусто = не менять; заполните, если Ozon пишет 'не заполнен обязательный атрибут ТН ВЭД')</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Хэштеги / ключевые слова (через запятую, пусто = не менять)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -540,6 +546,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -576,6 +583,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -601,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-y/7394698654.jpg|https://ir.ozone.ru/s3/multimedia-1-g/7940506156.jpg|https://ir.ozone.ru/s3/multimedia-1-c/7940505936.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -612,6 +620,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -648,6 +657,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -673,7 +683,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-s/7397498764.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -684,6 +694,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -720,6 +731,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -756,6 +768,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -792,6 +805,7 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -828,6 +842,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -864,6 +879,7 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -900,6 +916,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #dsg_ремонт #dsg_обслуживание #dq2000amdsg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -936,6 +957,7 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -961,7 +983,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-n/7770051311.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -972,6 +994,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1008,6 +1031,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1044,6 +1068,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg7 #dsg7_dq200 #dsg7_mechatronic #электроннаяплатаdq200</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1080,6 +1109,7 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1105,7 +1135,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-tmp-6/item-pic-2a3c594b7813848476bc066f768e0f1d.jpg|https://ir.ozone.ru/s3/multimedia-tmp-3/item-pic-16e5a96e917465720f68d39bec57e767.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.jpg</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1116,6 +1146,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1152,6 +1183,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1188,6 +1220,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1224,6 +1257,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1260,6 +1294,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1296,6 +1331,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1321,7 +1357,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-c/8458091220.jpg|https://ir.ozone.ru/s3/multimedia-1-d/10217930269.jpg|https://ir.ozone.ru/s3/multimedia-1-g/11484619324.jpg|https://ir.ozone.ru/s3/multimedia-1-0/10217896452.jpg|https://ir.ozone.ru/s3/multimedia-1-v/10217896051.jpg|https://ir.ozone.ru/s3/multimedia-1-u/10217896230.jpg|https://ir.ozone.ru/s3/multimedia-1-b/10217896103.jpg|https://ir.ozone.ru/s3/multimedia-1-8/10217986964.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.jpg</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1332,6 +1368,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #мехатроник_dq200 #dsg7 #dsg7_dq200 #dsg7_0am_dq200 #0am325066ae #0am325066ac #0am325066 #dq200ремкомплект #0am325025 #0am325025d</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1368,6 +1409,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1404,6 +1450,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1440,6 +1487,11 @@
           <t>8708409109 - Коробки передач и их части штампов.из стали, прочие</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1476,6 +1528,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1512,6 +1565,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1548,6 +1602,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1584,6 +1643,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1620,6 +1680,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1645,7 +1706,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-g/7768630888.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1656,6 +1717,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1692,6 +1754,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1717,7 +1780,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-w/9080035556.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.jpg</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1728,6 +1791,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1764,6 +1828,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1789,7 +1854,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-p/8577082285.jpg|https://ir.ozone.ru/s3/multimedia-1-2/8594712290.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1800,6 +1865,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1836,6 +1906,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1872,6 +1943,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1908,6 +1980,7 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1933,7 +2006,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7563423914.jpg|https://ir.ozone.ru/s3/multimedia-1-e/7552645178.jpg|https://ir.ozone.ru/s3/multimedia-1-g/7559287072.jpg|https://ir.ozone.ru/s3/multimedia-1-b/7559348411.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1944,6 +2017,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1980,6 +2054,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2016,6 +2091,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2052,6 +2132,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2088,6 +2169,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2124,6 +2206,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2149,7 +2232,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-f/8529361611.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -2160,6 +2243,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdsg7dq200</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2196,6 +2284,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкиdq200</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2221,7 +2314,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-m/8529439774.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -2232,6 +2325,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200dsg</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2268,6 +2366,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2304,6 +2407,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2329,7 +2433,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-q/7418270474.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2340,6 +2444,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2376,6 +2481,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2412,6 +2518,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2437,7 +2544,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-f/10611206151.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2448,6 +2555,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf011e</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2484,6 +2596,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2520,6 +2637,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2556,6 +2674,7 @@
           <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
+      <c r="K58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2592,6 +2711,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2617,7 +2737,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-8/8529468164.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2628,6 +2748,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2653,7 +2778,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-o/8529557856.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2664,6 +2789,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2689,7 +2815,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-9/14860646217.jpg|https://ir.ozone.ru/s3/multimedia-1-0/14860646604.jpg|https://ir.ozone.ru/s3/multimedia-1-b/14860761059.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2700,6 +2826,7 @@
           <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2736,6 +2863,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>#корпусмасляногофильтраEA888</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2761,7 +2893,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-1/10267723873.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888gen3_1.jpg</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2772,6 +2904,7 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
+      <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2808,6 +2941,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2844,6 +2978,7 @@
           <t>8421230000 - Оборудование и устройства для фильтрования масла или топлива в двигателях внутреннего сгорания</t>
         </is>
       </c>
+      <c r="K66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2880,6 +3015,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2905,7 +3041,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://ir.ozone.ru/s3/multimedia-1-8/7625693852.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -2916,6 +3052,7 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
+      <c r="K68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2948,9 +3085,10 @@
           <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
+      <c r="K69" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J69"/>
+  <autoFilter ref="A1:K69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -519,12 +519,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий</t>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X301127C</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -556,12 +556,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод</t>
+          <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -593,12 +593,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DQ250 02E DSG6</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество</t>
+          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -630,12 +630,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева</t>
+          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -667,12 +667,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП DSG7 DQ200 0AM 0CW</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -704,12 +704,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG 7 DQ200 0AM 0CW регулятор давления 1 шт</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325025B.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -741,12 +741,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM 0CW 1 шт</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -778,12 +778,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!</t>
+          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -815,12 +815,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр</t>
+          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -889,12 +889,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника с утолщением DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.</t>
+          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -930,12 +930,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG сепараторная пластина под плиту мехатроника DSG7 DQ200 0am 0cw</t>
+          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Прокладки платы DSG7 DQ200 0AM 0CW</t>
+          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 с прокладками и гидроплитой Плита, сальники, уплотнения</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200 0AM 0CW 2 пыльника 2 сальника 2 крышки</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов</t>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 подходит на ВСЕ DQ200 0am 0cw</t>
+          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.</t>
+          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 c эл. платой 0AM927769D в сборе</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!</t>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
+          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025P.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG крышка мехатроника DSG7 + Усиленная с утолщением прокладка крышки dq200</t>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках</t>
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Болты мехатроника DSG7DQ200 (0AM/0CW) комплект 7 шт. (4 M890 WHT001922 + 3 M835 WHT001922/01X301127C</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии</t>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200 (0AM 0CW) сальник, пыльник, крышка</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 dq200 оригинал VAG сепараторная пластина мехатроника + пластины на соленоиды</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)</t>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект: длинный шток 101мм 0AM325091E + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025u.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM Новые соленоиды Bosch</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.</t>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091F 99 мм + втулка (гильза) мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект: короткий шток 99мм 0AM325091F + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат</t>
+          <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025z.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025С.&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Сальник манжет штока сцепления мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0AM325091E</t>
+          <t>Шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!</t>
+          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 0AM 0CW 0am325091f (99 мм) короткий 1шт</t>
+          <t>Шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!</t>
+          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM325477AE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников DSG7 DQ200 0AM 0CW, 10 шт оригинал NSK, для VW / Audi / Skoda</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!</t>
+          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы 0am 0cw dq200 dsg 7</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыльники и сальники W</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;</t>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение резиновое электромотора гидроблока (мехатроника) DQ200 0AM DSG 7</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !</t>
+          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы электронной мехатроника DSG7 DQ200 0am 0cw</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.</t>
+          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Сальник штока мехатроника DSG7 DQ200 0AM / 0CW оригинал Volkswagen</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал Volkswagen Германия</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG 7 0B5 DL501 (123014 AF), аналог 0B5 325 421 для N436 / N440, Audi Q5 A4 A5</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E Старое поколение (RE0F10A) 2 датчика</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e</t>
+          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, Renault, Mitsubishi Новый</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор</t>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT для Nissan, Renault, Mitsubishi</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan</t>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 / 5636119 для Chevrolet, Opel (Astra J, Insignia, Cruze, Aveo)</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DSG7 DQ500 0BH</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла</t>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса мехатроника (гидроблока) DQ200 0AM DSG 7</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!</t>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Прокладки DQ200 DSG7+сальники и пыльники Оригинал Германия Volkswagen</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра EA888</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>EA888 Gen.3 магнит + корпус алюминиевый комплект</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!</t>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen 3</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E / RE0F10A вариатора CVT, 4 шт оригинал NSK для Nissan Mitsubishi Renault</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3062,10 +3062,14 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Накладка на автомобиль на педали, 3 шт.</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
+        </is>
+      </c>
       <c r="D69" s="2" t="n">
         <v>950</v>
       </c>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_7.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -983,7 +983,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_3.png</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_6.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_5.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$K$69</definedName>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1879</v>
+        <v>1450</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3000</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1479</v>
+        <v>999</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>2500</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9479</v>
+        <v>4950</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>12000</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>999</v>
+        <v>850</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1500</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1479</v>
+        <v>1450</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>2000</v>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1990</v>
+        <v>1450</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>3000</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1990</v>
+        <v>1240</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>3500</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3479</v>
+        <v>1250</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>4500</v>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>979</v>
+        <v>850</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>2000</v>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2879</v>
+        <v>1950</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8979</v>
+        <v>4850</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>12000</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>979</v>
+        <v>850</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1800</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1479</v>
+        <v>1240</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>2500</v>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>979</v>
+        <v>879</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>2000</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1479</v>
+        <v>1250</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>2500</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>2000</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>8879</v>
+        <v>7450</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>10000</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2879</v>
+        <v>1950</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2879</v>
+        <v>1950</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM325477AE</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2479</v>
+        <v>490</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>4000</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>931</v>
+        <v>850</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>979</v>
+        <v>850</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1500</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1290</v>
+        <v>850</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>2000</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1490</v>
+        <v>1240</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>2500</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1490</v>
+        <v>1240</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>2500</v>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>5879</v>
+        <v>3850</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>8890</v>
+        <v>8450</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>12000</v>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3879</v>
+        <v>2950</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>6000</v>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>1500</v>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1450</v>
+        <v>1879</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3000</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>999</v>
+        <v>1479</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>2500</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>850</v>
+        <v>999</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1500</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1450</v>
+        <v>1479</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>2000</v>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1450</v>
+        <v>1990</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>3000</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1240</v>
+        <v>1990</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>3500</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1250</v>
+        <v>3479</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>4500</v>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1950</v>
+        <v>2879</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4850</v>
+        <v>8979</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>12000</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>850</v>
+        <v>979</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1800</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1240</v>
+        <v>1479</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>2500</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1250</v>
+        <v>1479</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>2500</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>950</v>
+        <v>979</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>2000</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7450</v>
+        <v>8879</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>10000</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1950</v>
+        <v>2879</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1950</v>
+        <v>2879</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>490</v>
+        <v>2479</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>4000</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>850</v>
+        <v>1290</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>2000</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1240</v>
+        <v>1490</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>2500</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1240</v>
+        <v>1490</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>2500</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>8450</v>
+        <v>8890</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>12000</v>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2950</v>
+        <v>3879</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>6000</v>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="n"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$K$69</definedName>
@@ -539,7 +539,9 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="3" t="n"/>
+      <c r="H2" s="3" t="n">
+        <v>90</v>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -576,7 +578,9 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -613,7 +617,9 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -650,7 +656,9 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="n">
+        <v>87</v>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -687,7 +695,9 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -724,7 +734,9 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -761,7 +773,9 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n">
+        <v>19</v>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -798,7 +812,9 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -835,7 +851,9 @@
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="n">
+        <v>83</v>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -872,7 +890,9 @@
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="n">
+        <v>87</v>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -909,7 +929,9 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="n">
+        <v>51</v>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -950,7 +972,9 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="n">
+        <v>35</v>
+      </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -987,7 +1011,9 @@
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1024,7 +1050,9 @@
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="n">
+        <v>28</v>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1089,9 @@
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1102,7 +1132,9 @@
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="n">
+        <v>51</v>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1139,7 +1171,9 @@
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1176,7 +1210,9 @@
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1213,7 +1249,9 @@
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1250,7 +1288,9 @@
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1287,7 +1327,9 @@
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="n">
+        <v>74</v>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -1324,7 +1366,9 @@
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="n">
+        <v>93</v>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1405,9 @@
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1448,9 @@
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1491,9 @@
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="n">
+        <v>69</v>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -1480,7 +1530,9 @@
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="n">
+        <v>31</v>
+      </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -1521,7 +1573,9 @@
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="n">
+        <v>43</v>
+      </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -1558,7 +1612,9 @@
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="n">
+        <v>93</v>
+      </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -1595,7 +1651,9 @@
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -1636,7 +1694,9 @@
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n">
+        <v>86</v>
+      </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -1673,7 +1733,9 @@
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="n">
+        <v>74</v>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -1710,7 +1772,9 @@
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -1747,7 +1811,9 @@
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="n">
+        <v>53</v>
+      </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1850,9 @@
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="n">
+        <v>36</v>
+      </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1889,9 @@
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="n">
+        <v>82</v>
+      </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -1858,7 +1928,9 @@
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1971,9 @@
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="n">
+        <v>47</v>
+      </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -1936,7 +2010,9 @@
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -1973,7 +2049,9 @@
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -2010,7 +2088,9 @@
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="n">
+        <v>21</v>
+      </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -2047,7 +2127,9 @@
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -2084,7 +2166,9 @@
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="n">
+        <v>40</v>
+      </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -2125,7 +2209,9 @@
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="n">
+        <v>29</v>
+      </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -2162,7 +2248,9 @@
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -2199,7 +2287,9 @@
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -2236,7 +2326,9 @@
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -2277,7 +2369,9 @@
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -2318,7 +2412,9 @@
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -2359,7 +2455,9 @@
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="n">
+        <v>53</v>
+      </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -2400,7 +2498,9 @@
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -2437,7 +2537,9 @@
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="n">
+        <v>32</v>
+      </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -2474,7 +2576,9 @@
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="n">
+        <v>36</v>
+      </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -2511,7 +2615,9 @@
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="n">
+        <v>28</v>
+      </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -2548,7 +2654,9 @@
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -2589,7 +2697,9 @@
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -2630,7 +2740,9 @@
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2779,9 @@
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="n">
+        <v>37</v>
+      </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -2704,7 +2818,9 @@
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -2741,7 +2857,9 @@
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -2782,7 +2900,9 @@
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="n">
+        <v>77</v>
+      </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -2819,7 +2939,9 @@
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -2856,7 +2978,9 @@
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="n">
+        <v>19</v>
+      </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -2897,7 +3021,9 @@
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -2934,7 +3060,9 @@
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -2971,7 +3099,9 @@
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -3008,7 +3138,9 @@
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="n">
+        <v>93</v>
+      </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -3045,7 +3177,9 @@
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -3082,7 +3216,9 @@
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$K$69</definedName>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1180,7 +1180,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1182,7 +1182,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
         </is>
       </c>
     </row>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$K$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$K$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -631,72 +631,74 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+          <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3879</v>
+        <v>118000</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5000</v>
+        <v>145000</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E927770AL_1.png</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="3" t="n">
-        <v>87</v>
-      </c>
+      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
+          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1479</v>
+        <v>3879</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="3" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
@@ -709,33 +711,33 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325025B.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4950</v>
+        <v>1479</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12000</v>
+        <v>2500</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
@@ -748,33 +750,33 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) &lt;br/&gt;&lt;br/&gt;Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>999</v>
+        <v>9479</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1500</v>
+        <v>12000</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
@@ -787,38 +789,38 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3479</v>
+        <v>999</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="3" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -826,38 +828,38 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
+          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>999</v>
+        <v>3479</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="3" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -865,38 +867,38 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1479</v>
+        <v>999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="3" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -904,33 +906,33 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1990</v>
+        <v>1479</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="3" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
@@ -938,42 +940,38 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #dsg_ремонт #dsg_обслуживание #dq2000amdsg</t>
-        </is>
-      </c>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
+          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
         <v>1990</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="3" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
@@ -981,43 +979,47 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #dsg_ремонт #dsg_обслуживание #dq2000amdsg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
+          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11979</v>
+        <v>1990</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -1025,33 +1027,33 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8890</v>
+        <v>11979</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
@@ -1064,76 +1066,72 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>78800</v>
+        <v>8890</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>80000</v>
+        <v>12000</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg7 #dsg7_dq200 #dsg7_mechatronic #электроннаяплатаdq200</t>
-        </is>
-      </c>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3479</v>
+        <v>78800</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4500</v>
+        <v>80000</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="3" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
@@ -1141,55 +1139,55 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg7 #dsg7_dq200 #dsg7_mechatronic #электроннаяплатаdq200</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>3879</v>
+        <v>3479</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
-        </is>
-      </c>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1199,23 +1197,23 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7979</v>
+        <v>3879</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_3.png</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
@@ -1223,22 +1221,26 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1249,12 +1251,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
@@ -1267,33 +1269,33 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>12890</v>
+        <v>7979</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
@@ -1306,33 +1308,33 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2890</v>
+        <v>12890</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
@@ -1345,33 +1347,33 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3879</v>
+        <v>2890</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="3" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
@@ -1384,76 +1386,72 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>68800</v>
+        <v>3879</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>90000</v>
+        <v>6000</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="3" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #мехатроник_dq200 #dsg7 #dsg7_dq200 #dsg7_0am_dq200 #0am325066ae #0am325066ac #0am325066 #dq200ремкомплект #0am325025 #0am325025d</t>
-        </is>
-      </c>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
+          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>128800</v>
+        <v>68800</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>150000</v>
+        <v>90000</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.jpg</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
@@ -1463,161 +1461,165 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+          <t>#dq200 #мехатроник_dq200 #dsg7 #dsg7_dq200 #dsg7_0am_dq200 #0am325066ae #0am325066ac #0am325066 #dq200ремкомплект #0am325025 #0am325025d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025P.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>850</v>
+        <v>128800</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2000</v>
+        <v>150000</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="3" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.&lt;br/&gt;&lt;br/&gt;Клипса штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Устанавливается внутрь штока</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4879</v>
+        <v>979</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_2.png</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="3" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8708409109 - Коробки передач и их части штампов.из стали, прочие</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
-        </is>
-      </c>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3879</v>
+        <v>4879</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="3" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>8708409109 - Коробки передач и их части штампов.из стали, прочие</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>0am325025h</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1990</v>
+        <v>3879</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_6.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="3" t="n">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
@@ -1630,115 +1632,115 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025h</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2879</v>
+        <v>1990</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_6.png</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
-        </is>
-      </c>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1490</v>
+        <v>2879</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2300</v>
+        <v>5000</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="3" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
+          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>8879</v>
+        <v>1490</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12000</v>
+        <v>2300</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="3" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
@@ -1751,33 +1753,33 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8979</v>
+        <v>8879</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>12000</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.png</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="3" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
@@ -1790,33 +1792,33 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>979</v>
+        <v>8979</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1800</v>
+        <v>12000</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="3" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
@@ -1829,33 +1831,33 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1479</v>
+        <v>979</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.png</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="3" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
@@ -1868,33 +1870,33 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: длинный шток 101мм 0AM325091E + втулка мехатроника DSG7 DQ200</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025u.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4490</v>
+        <v>1479</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="3" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
@@ -1907,33 +1909,33 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>78475</v>
+        <v>4490</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>90000</v>
+        <v>6000</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
@@ -1941,42 +1943,38 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
-        </is>
-      </c>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект: короткий шток 99мм 0AM325091F + втулка мехатроника DSG7 DQ200</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025z.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4490</v>
+        <v>78475</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>6000</v>
+        <v>90000</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="3" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
@@ -1984,38 +1982,42 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025С.&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>879</v>
+        <v>4490</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="3" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
@@ -2028,38 +2030,38 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
+          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1479</v>
+        <v>979</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -2067,38 +2069,38 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>979</v>
+        <v>1479</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
@@ -2106,33 +2108,33 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>8879</v>
+        <v>979</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="3" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
@@ -2145,33 +2147,33 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм (новый тип)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2879</v>
+        <v>8879</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="3" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
@@ -2179,26 +2181,22 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>#dq200 #dsg7</t>
-        </is>
-      </c>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>🔩 Шток мехатроника DSG7 DQ200 — 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм (до 2012 г.)&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2209,12 +2207,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
@@ -2222,77 +2220,83 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2479</v>
+        <v>8850</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_1.png</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>#dq200 #dsg7</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
+          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>11979</v>
+        <v>2879</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
@@ -2305,76 +2309,70 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>850</v>
+        <v>8850</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="3" t="n">
-        <v>49</v>
-      </c>
+      <c r="H47" s="3" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdsg7dq200</t>
-        </is>
-      </c>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>16890</v>
+        <v>2479</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>25000</v>
+        <v>4000</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="3" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
@@ -2382,42 +2380,38 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкиdq200</t>
-        </is>
-      </c>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
+          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП&lt;ul&gt;&lt;li&gt;Оригинальное качество NSK&lt;/li&gt;&lt;li&gt;10 шт в комплекте – полная замена&lt;/li&gt;&lt;/ul&gt;Добавляйте в корзину!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0ambset.</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>850</v>
+        <v>11979</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1500</v>
+        <v>15000</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="3" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
@@ -2425,42 +2419,38 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdq200dsg</t>
-        </is>
-      </c>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1290</v>
+        <v>931</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="3" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
@@ -2470,40 +2460,40 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+          <t>#Прокладкаdsg7dq200</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1490</v>
+        <v>16890</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2500</v>
+        <v>25000</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
@@ -2511,38 +2501,42 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкиdq200</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>979</v>
+        <v>850</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="3" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
@@ -2550,38 +2544,42 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200dsg</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1490</v>
+        <v>1290</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="3" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
@@ -2589,38 +2587,42 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1479</v>
+        <v>1490</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
@@ -2633,76 +2635,72 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>58900</v>
+        <v>979</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>80000</v>
+        <v>1500</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>#гидроблокjf011e</t>
-        </is>
-      </c>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>58900</v>
+        <v>1490</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>80000</v>
+        <v>2500</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
@@ -2710,42 +2708,38 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
-        </is>
-      </c>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>58900</v>
+        <v>1479</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>80000</v>
+        <v>2500</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
@@ -2758,72 +2752,76 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
+          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>999</v>
+        <v>58900</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2000</v>
+        <v>80000</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="3" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf011e</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>3850</v>
+        <v>58900</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>8000</v>
+        <v>80000</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
@@ -2831,38 +2829,42 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>#гидроблокjf015e #гидроблоквариатораjf015e #гидроблокcvtjf015e</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>979</v>
+        <v>58900</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1500</v>
+        <v>80000</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
@@ -2870,47 +2872,43 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>#Прокладкаdq200</t>
-        </is>
-      </c>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>8890</v>
+        <v>999</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="3" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
@@ -2918,38 +2916,36 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3879</v>
+        <v>19800</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>6000</v>
+        <v>25000</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.png</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="3" t="n">
-        <v>30</v>
-      </c>
+      <c r="H62" s="3" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
@@ -2957,33 +2953,33 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра двигателя EA888</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>4741</v>
+        <v>3850</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="3" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
@@ -2991,81 +2987,81 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>#корпусмасляногофильтраEA888</t>
-        </is>
-      </c>
+      <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>6690</v>
+        <v>979</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888gen3_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2366</v>
+        <v>8890</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>3500</v>
+        <v>12000</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="3" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
@@ -3078,38 +3074,38 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Тестовый товар не публикуется</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>100</v>
+        <v>3879</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>8421230000 - Оборудование и устройства для фильтрования масла или топлива в двигателях внутреннего сгорания</t>
+          <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
@@ -3117,33 +3113,33 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+          <t>Корпус масляного фильтра двигателя EA888</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>979</v>
+        <v>4741</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="3" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
@@ -3151,43 +3147,47 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>#корпусмасляногофильтраEA888</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>Комплект как на фото алюминиевый корпус EA888 + магните gen.3 &lt;br/&gt;&lt;br/&gt;Отличное качество алюминия и магнита (хорошо улавливает частицы)&lt;br/&gt;&lt;br/&gt;Комплектом дешевле, заказывайте!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: EA888gen3.</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>12979</v>
+        <v>6690</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888gen3_1.jpg</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
@@ -3195,44 +3195,1499 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+          <t>Магнит на корпус масляного фильтра EA888 Gen.3</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>990</v>
+        <v>2366</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Тестовый товар не публикуется</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Тестовая карточка для проверки автоматизации, будет удалена после теста</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>8421230000 - Оборудование и устройства для фильтрования масла или топлива в двигателях внутреннего сгорания</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>WHT001922</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1490</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.png</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>gidroakkumulyator-orig</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>8890</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>jf011e</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>12979</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>klipsy-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.png</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>3879</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>nakladki-pedali</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Накладки на педали автомобиля, 3 шт, резиновые</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Комплект накладок на педали автомобиля — 3 шт (газ, тормоз, сцепление/подножка). ✅ Подходит универсально на большинство легковых автомобилей с механической коробкой (Volkswagen, Audi, Škoda и другие). 📦 В комплекте 3 накладки. ⭐ Защищают штатные педали от истирания, улучшают сцепление подошвы обуви с педалью в сырую погоду.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>990</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.png</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
           <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>planka-solenoid-2sht</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2890</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.png</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-orig</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>990</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.png</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.png</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.png</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig-v2</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.png</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.png</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.png</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>1490</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.png</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig-v2</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1490</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>2490</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_2.png</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1690</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.png</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.png</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.png</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>salnikprivod-l</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Сальник привода левый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.png</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Сальник привода правый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.png</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Сальник входного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.png</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Сальник выходного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.png</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.png</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>8900</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.png</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>4990</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.png</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>8708409909 - Части коробок передач, прочие: прочие</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K69"/>
+  <autoFilter ref="A1:K108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1632,7 +1632,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>0am325025h</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1653,13 +1653,11 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025h_6.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="3" t="n">
-        <v>93</v>
-      </c>
+      <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -1692,7 +1690,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1735,7 +1733,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1774,7 +1772,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1813,7 +1811,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1852,7 +1850,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -2207,7 +2205,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -2291,7 +2289,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -2367,7 +2365,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2488,7 +2486,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025-2.png</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2574,7 +2572,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2974,7 +2972,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -3370,7 +3368,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$K$108</definedName>
@@ -524,7 +524,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -548,7 +548,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -563,7 +567,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+          <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -587,7 +591,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -602,7 +610,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -626,7 +634,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -682,7 +694,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag.</t>
+          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -706,7 +718,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -721,7 +737,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -745,7 +761,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>заглушка dq200, заглушка дсг 7, заглушка кпп dq200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -799,7 +819,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.&lt;br/&gt;🔎 Также ищут: заглушка dq200, заглушка дсг 7, заглушка кпп dq200.</t>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -823,7 +843,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>заглушка dq200, заглушка дсг 7, заглушка кпп dq200</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -838,7 +862,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200.</t>
+          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -862,7 +886,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -877,7 +905,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.&lt;br/&gt;🔎 Также ищут: сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200.</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -901,7 +929,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -916,7 +948,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -940,7 +972,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -955,7 +991,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -981,7 +1017,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #dsg_ремонт #dsg_обслуживание #dq2000amdsg</t>
+          <t>прокладка dq200, прокладки dq200, прокладка мехатроника dq200</t>
         </is>
       </c>
     </row>
@@ -998,7 +1034,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: сепараторная пластина dq200, сепараторная пластина dsg 7.</t>
+          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1022,7 +1058,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>сепараторная пластина dq200, сепараторная пластина dsg 7</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1037,7 +1077,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1061,7 +1101,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1076,7 +1120,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7.</t>
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1100,7 +1144,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1115,7 +1163,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1141,7 +1189,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg7 #dsg7_dq200 #dsg7_mechatronic #электроннаяплатаdq200</t>
+          <t>плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1206,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1182,7 +1230,11 @@
           <t>8708405001 - Части и принадлежности моторных транспортных средств товарных позиций 8701 – 8705: коробки передач и их части: прочие: коробки передач: для промышленной сборки моторных транспортных средств товарных позиций 8701 – 8705, кроме моторных транспортных средств, упомянутых в подсубпозиции 8708 40 200; для промышленной сборки узлов и агрегатов моторных транспортных средств товарных позиций</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1240,7 +1292,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1264,7 +1316,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1279,7 +1335,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1303,7 +1359,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1318,7 +1378,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1342,7 +1402,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1357,7 +1421,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1381,7 +1445,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1396,7 +1464,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1420,7 +1488,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1478,7 +1550,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -1504,7 +1576,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>#dq200 #dq200ремкомплект #dsg7 #dsg7_dq200 #0am325066ae #0am325066ac #0am325066 #ocw #0am325066ae #0am</t>
+          <t>плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1632,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1586,7 +1658,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>#dq200 #dq200ремкомплект #dq200_0am #dsg #dsg7 #dsg_ремонт #dsg_обслуживание #dsg0amразборка #dsg_трансмиссия #dsg_7</t>
+          <t>прокладка dq200, прокладки dq200, прокладка мехатроника dq200</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1675,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1627,7 +1699,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1642,7 +1718,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.&lt;br/&gt;🔎 Также ищут: пыльник штока dq200, сальник штока dq200, ремкомплект dq200.</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1664,7 +1740,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>пыльник штока dq200, сальник штока dq200, ремкомплект dq200</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1679,7 +1759,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.&lt;br/&gt;🔎 Также ищут: прокладка dq200, прокладки dq200, прокладка мехатроника dq200.</t>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -1705,7 +1785,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>#dsg #dsg7 #dsg_ремонт #dsg_7 #dsg_трансмиссия #dsg0amразборка #dsg7_dq200 #dsg7_0am_dq200 #dsg7_dq200_0am #dsg7dq200 #dsg7скоростей #dsg7_mechatronic</t>
+          <t>прокладка dq200, прокладки dq200, прокладка мехатроника dq200</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1841,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, прокладка dq200, прокладки dq200.</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -1785,7 +1865,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект dq200, прокладка dq200, прокладки dq200</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1800,7 +1884,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -1824,7 +1908,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1839,7 +1927,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -1863,7 +1951,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1878,7 +1970,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.&lt;br/&gt;🔎 Также ищут: толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7.</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -1902,7 +1994,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1917,7 +2013,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -1941,7 +2037,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1956,7 +2056,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -1982,7 +2082,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>#Мехатроникdsg7 #Мехатроникdq200</t>
+          <t>соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2099,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного! &lt;br/&gt;&lt;br/&gt;🔎 Также ищут: ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200.</t>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного!</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2023,7 +2123,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2116,7 +2220,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2140,7 +2244,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>сальник штока dq200, сальники штоков dq200, сальник штока dsg 7</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2155,7 +2263,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200.</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2179,7 +2287,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2194,7 +2306,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2220,7 +2332,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>#dq200 #dsg7</t>
+          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2390,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -2302,7 +2414,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2354,7 +2470,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.&lt;br/&gt;🔎 Также ищут: соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7.</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2378,7 +2494,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2475,7 +2595,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.&lt;br/&gt;🔎 Также ищут: пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200.</t>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2501,7 +2621,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкиdq200</t>
+          <t>пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2681,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.&lt;br/&gt;🔎 Также ищут: плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200.</t>
+          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2587,7 +2707,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>#Прокладкаэлектроннойплатыdsg #DSG7DQ200 #0am927377 #прокладкамехатроникаDSG7</t>
+          <t>плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2724,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.&lt;br/&gt;🔎 Также ищут: сальник штока dq200, сальники штоков dq200, сальник штока dsg 7.</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -2628,7 +2748,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>сальник штока dq200, сальники штоков dq200, сальник штока dsg 7</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2643,7 +2767,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -2667,7 +2791,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2682,7 +2810,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.&lt;br/&gt;🔎 Также ищут: шток dq200, штоки dq200, штоки мехатроника dq200.</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -2706,7 +2834,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2721,7 +2853,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500.</t>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -2745,7 +2877,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2885,7 +3021,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200.</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -2909,7 +3045,11 @@
           <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2961,7 +3101,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -2985,7 +3125,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3043,7 +3187,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.&lt;br/&gt;🔎 Также ищут: прокладка dq200, пыльники штоков dq200, сальники штоков dq200.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -3067,7 +3211,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>прокладка dq200, пыльники штоков dq200, сальники штоков dq200</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3082,7 +3230,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: фильтр dq500, корпус фильтра dq500, масляный фильтр dq500.</t>
+          <t>Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)&lt;br/&gt;&lt;br/&gt;Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.&lt;br/&gt;&lt;br/&gt;✅ Подходит для:&lt;br/&gt;&lt;br/&gt;• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением&lt;br/&gt;&lt;br/&gt;• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0BH325183B, 0BH325159&lt;br/&gt;&lt;br/&gt;💡 Почему стоит взять:&lt;br/&gt;&lt;br/&gt;• Устойчив к перегреву и механическим нагрузкам&lt;br/&gt;&lt;br/&gt;• В комплекте уплотнительное кольцо&lt;br/&gt;&lt;br/&gt;• Простая установка без доработки&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -3106,7 +3254,11 @@
           <t>8708999709 - Прочие части и принадлежности моторных транспортных средств товарных позиций 8701 - 8705, прочие, прочие</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3121,7 +3273,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+          <t>Усиленный алюминиевый корпус масляного фильтра для двигателей EA888 заменяет штатный пластиковый корпус, который со временем становится хрупким и склонен к растрескиванию. Алюминиевый корпус обеспечивает высокую механическую прочность, устойчивость к нагреву и долговечность.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Повышенная прочность по сравнению с заводским пластиковым корпусом.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к высоким температурам.&lt;br/&gt;&lt;br/&gt;	•	Улучшенный отвод тепла от зоны фильтра.&lt;br/&gt;&lt;br/&gt;	•	Полная совместимость с оригинальными масляными фильтрами.&lt;br/&gt;&lt;br/&gt;	•	Простая установка без доработок.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для двигателей EA888 Gen 1/2/3 (1.8 TSI и 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda, SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра  +уплотнительное кольцо!</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -3147,7 +3299,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>#корпусмасляногофильтраEA888</t>
+          <t>корпус фильтра ea888</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3355,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра&lt;br/&gt;&lt;br/&gt;🔎 Также ищут: корпус фильтра ea888.</t>
+          <t>Магнит для установки на корпус масляного фильтра двигателей EA888 Gen 3. Предназначен для улавливания металлических частиц, циркулирующих в моторном масле, что снижает износ деталей двигателя и повышает эффективность смазочной системы. Используется как дополнительная мера защиты двигателя.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Удерживает мелкие металлические частицы внутри фильтрующего элемента.&lt;br/&gt;&lt;br/&gt;	•	Снижает износ во много раз! - бюджетное решение для продления срока службы двигателя! &lt;br/&gt;&lt;br/&gt;	•	Работает совместно со штатным масляным фильтром.&lt;br/&gt;&lt;br/&gt;	•	Простая установка на корпус фильтра или рядом с ним.&lt;br/&gt;&lt;br/&gt;	•	Устойчивость к маслу и высоким температурам.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Двигатели EA888 Gen 3 (1.8 TSI, 2.0 TSI) на автомобилях Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;Магнитный элемент для корпуса фильтра</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
@@ -3227,7 +3379,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>корпус фильтра ea888</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3281,7 +3437,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.&lt;br/&gt;🔎 Также ищут: болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200.</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -3305,7 +3461,11 @@
           <t>8708409909 - Части коробок передач, прочие: прочие</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200</t>
+          <t>#болты_мехатроника_dq200 #болт_мехатроника_dq200 #затяжка_болтов_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag</t>
+          <t>#фильтр_02e305051c #02e305051c_фильтр_масляный #02e305051c_фильтр_масляный_vag</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag</t>
+          <t>#фильтр_02e305051c #02e305051c_фильтр_масляный #02e305051c_фильтр_масляный_vag</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>фильтр 02e305051c, 02e305051c фильтр масляный, 02e305051c фильтр масляный vag</t>
+          <t>#фильтр_02e305051c #02e305051c_фильтр_масляный #02e305051c_фильтр_масляный_vag</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>заглушка dq200, заглушка дсг 7, заглушка кпп dq200</t>
+          <t>#заглушка_dq200 #заглушка_дсг_7 #заглушка_кпп_dq200</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>заглушка dq200, заглушка дсг 7, заглушка кпп dq200</t>
+          <t>#заглушка_dq200 #заглушка_дсг_7 #заглушка_кпп_dq200</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>крышка мехатроника dq200, прокладка крышки dq200, прокладка крышки мехатроника dq200</t>
+          <t>#крышка_мехатроника_dq200 #прокладка_крышки_dq200 #прокладка_крышки_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>сальники толкателей дсг 7, сальники толкателей dq200, сальники толкателей вилок dq200</t>
+          <t>#сальники_толкателей_дсг_7 #сальники_толкателей_dq200 #сальники_толкателей_вилок_dq200</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500</t>
+          <t>#фильтр_мехатроника_dq200 #корпус_фильтра_dsg_dq500 #фильтр_dsg_7_dq500</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>прокладка dq200, прокладки dq200, прокладка мехатроника dq200</t>
+          <t>#прокладка_dq200 #прокладки_dq200 #прокладка_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>сепараторная пластина dq200, сепараторная пластина dsg 7</t>
+          <t>#сепараторная_пластина_dq200 #сепараторная_пластина_dsg_7</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7</t>
+          <t>#соленоид_регулятор_давления_дсг7 #регулятор_давления_мехатроника_дсг_7_соленоид #соленоид_регулятор_давления_дсг_7</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>гидроаккумулятор dq200, гидроаккумулятор дсг 7, гидроаккумулятор dsg 7</t>
+          <t>#гидроаккумулятор_dq200 #гидроаккумулятор_дсг_7 #гидроаккумулятор_dsg_7</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200</t>
+          <t>#плата_мехатроника_dq200 #плата_dsg_dq200 #плата_dsg_7_dq200</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200</t>
+          <t>#плата_мехатроника_dq200 #плата_dsg_dq200 #плата_dsg_7_dq200</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>ремкомплект dq200, ремкомплект мехатроника dq200, прокладка мехатроника dq200</t>
+          <t>#ремкомплект_dq200 #ремкомплект_мехатроника_dq200 #прокладка_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+          <t>#шток_dq200 #штоки_dq200 #штоки_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200</t>
+          <t>#пыльники_штоков_dq200 #сальники_штоков_dq200 #ремкомплект_dq200</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200</t>
+          <t>#плата_мехатроника_dq200 #плата_dsg_dq200 #плата_dsg_7_dq200</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>прокладка dq200, прокладки dq200, прокладка мехатроника dq200</t>
+          <t>#прокладка_dq200 #прокладки_dq200 #прокладка_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200</t>
+          <t>#болты_мехатроника_dq200 #болт_мехатроника_dq200 #затяжка_болтов_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>пыльник штока dq200, сальник штока dq200, ремкомплект dq200</t>
+          <t>#пыльник_штока_dq200 #сальник_штока_dq200 #ремкомплект_dq200</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>прокладка dq200, прокладки dq200, прокладка мехатроника dq200</t>
+          <t>#прокладка_dq200 #прокладки_dq200 #прокладка_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>ремкомплект dq200, прокладка dq200, прокладки dq200</t>
+          <t>#ремкомплект_dq200 #прокладка_dq200 #прокладки_dq200</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7</t>
+          <t>#соленоид_регулятор_давления_дсг7 #регулятор_давления_мехатроника_дсг_7_соленоид #соленоид_регулятор_давления_дсг_7</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+          <t>#шток_dq200 #штоки_dq200 #штоки_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>толкатели вилок dq200, размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200, сальники толкателей дсг 7</t>
+          <t>#толкатели_вилок_dq200 #размер_уплотнительного_кольца_ремонтного_гидроаккумулятора_dsg_dq200 #сальники_толкателей_дсг_7</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200</t>
+          <t>#ремкомплект_dq200 #ремкомплект_мехатроника_dq200 #шток_dq200</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7</t>
+          <t>#соленоид_регулятор_давления_дсг7 #регулятор_давления_мехатроника_дсг_7_соленоид #соленоид_регулятор_давления_дсг_7</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>ремкомплект dq200, ремкомплект мехатроника dq200, шток dq200</t>
+          <t>#ремкомплект_dq200 #ремкомплект_мехатроника_dq200 #шток_dq200</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>сальник штока dq200, сальники штоков dq200, сальник штока dsg 7</t>
+          <t>#сальник_штока_dq200 #сальники_штоков_dq200 #сальник_штока_dsg_7</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>гидроплита dq200, гидроплита dsg 7, гидроплита dsg dq200</t>
+          <t>#гидроплита_dq200 #гидроплита_dsg_7 #гидроплита_dsg_dq200</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+          <t>#шток_dq200 #штоки_dq200 #штоки_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+          <t>#шток_dq200 #штоки_dq200 #штоки_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>соленоид регулятор давления дсг7, регулятор давления мехатроника дсг 7 соленоид, соленоид регулятор давления дсг 7</t>
+          <t>#соленоид_регулятор_давления_дсг7 #регулятор_давления_мехатроника_дсг_7_соленоид #соленоид_регулятор_давления_дсг_7</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>пыльники штоков dq200, сальники штоков dq200, ремкомплект dq200</t>
+          <t>#пыльники_штоков_dq200 #сальники_штоков_dq200 #ремкомплект_dq200</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>плата мехатроника dq200, плата dsg dq200, плата dsg 7 dq200</t>
+          <t>#плата_мехатроника_dq200 #плата_dsg_dq200 #плата_dsg_7_dq200</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>сальник штока dq200, сальники штоков dq200, сальник штока dsg 7</t>
+          <t>#сальник_штока_dq200 #сальники_штоков_dq200 #сальник_штока_dsg_7</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+          <t>#шток_dq200 #штоки_dq200 #штоки_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>шток dq200, штоки dq200, штоки мехатроника dq200</t>
+          <t>#шток_dq200 #штоки_dq200 #штоки_мехатроника_dq200</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>фильтр мехатроника dq200, корпус фильтра dsg dq500, фильтр dsg 7 dq500</t>
+          <t>#фильтр_мехатроника_dq200 #корпус_фильтра_dsg_dq500 #фильтр_dsg_7_dq500</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200</t>
+          <t>#размер_уплотнительного_кольца_ремонтного_гидроаккумулятора_dsg_dq200</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>прокладка dq200, пыльники штоков dq200, сальники штоков dq200</t>
+          <t>#прокладка_dq200 #пыльники_штоков_dq200 #сальники_штоков_dq200</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>фильтр dq500, корпус фильтра dq500, масляный фильтр dq500</t>
+          <t>#фильтр_dq500 #корпус_фильтра_dq500 #масляный_фильтр_dq500</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>корпус фильтра ea888</t>
+          <t>#корпус_фильтра_ea888</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>корпус фильтра ea888</t>
+          <t>#корпус_фильтра_ea888</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>болты мехатроника dq200, болт мехатроника dq200, затяжка болтов мехатроника dq200</t>
+          <t>#болты_мехатроника_dq200 #болт_мехатроника_dq200 #затяжка_болтов_мехатроника_dq200</t>
         </is>
       </c>
     </row>

--- a/data/ozon_catalog.xlsx
+++ b/data/ozon_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ozon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ozon'!$A$1:$K$108</definedName>
@@ -535,7 +535,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png?v=3623a09a3d</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png?v=66392bb8b2</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png?v=853ce5f975|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E927770AL_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E927770AL_1.png?v=1ed880b735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -705,7 +705,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png?v=01ff072142|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png?v=5bada80f79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=7ea3564566|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png?v=925edc897f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png?v=2dddb3884d</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -873,7 +873,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png?v=23bde7d308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png?v=ef9e5c1565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png?v=8bec31bf8f</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png?v=558065bb93|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png?v=34e4e88bf6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png?v=e49b0e06dd</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=1d88443a00|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png?v=7dfb22192b</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.png?v=207791c0ab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.jpg?v=34d94b6ab7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_2.png?v=8522c1e191|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_3.png?v=a72d637b33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png?v=c5312dc0b8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png?v=92f41095e4</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png?v=ed43613b04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png?v=5a785335c2</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png?v=9a506331a9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png?v=45a69e38a1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png?v=4b4f837537|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png?v=e1488b6f03</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=936073c4cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png?v=4ec9bb8ca0|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png?v=838071f395|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png?v=b93ad38a77</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png?v=4f093a4b63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png?v=fc60a3cbb2</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png?v=42835ce71d</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=7cb0bd4a20</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png?v=9a4139b864</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png?v=2ec99b161d</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg?v=e0223e07fa</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png?v=04fb90265c</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png?v=462ec457c3</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png?v=c48648e856</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=a1c5e406d3</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png?v=3fb6a6ed69</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png?v=997df2de75</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png?v=9f571585c3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png?v=9fbf2bb6f0</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png?v=9e53670a82</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_1.png?v=39677a9dd4</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png?v=8cfd86455e</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png?v=6b39215af5</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png?v=51d4844731|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png?v=bcd5b49d99</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=9185e154b7</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025-2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png?v=b98621fc0a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png?v=e41c86e98b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025-2.png?v=45a69e38a1</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=9c731d1419</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png?v=ebfa02ae85</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png?v=ff168c7b41|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png?v=78bf59e6bd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png?v=71a27c560b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png?v=ce40d7f683</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg?v=dc356035c7</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png?v=6ac791003d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png?v=4bd4c0625c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png?v=4e011c48be</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png?v=c51183578d</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png?v=ee5f7fcab1</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.png?v=434a7e1a34</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=63685aa19d</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=34d94b6ab7</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.png?v=d699049a68</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888gen3_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888gen3_1.jpg?v=8c34e33dc7</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_1.png?v=ee750237ca|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Ea888gen3_2.png?v=4103d4f796</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TEST001_2.jpg?v=401765e5cb</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png?v=1d34e63372</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.png?v=995613c21a</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png?v=a21cf79b1b</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=648c289289</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.png?v=5d4d3c5107</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png?v=207791c0ab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png?v=33f6b91718</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.png?v=2f5de45272|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.png?v=892509e07d</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.png?v=cef8cc4537</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.png?v=9ce5d50d5b</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.png?v=16f48e3b34</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.png?v=b85e77777e</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.png?v=bcd5b49d99|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.png?v=51d4844731</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.png?v=b93ad38a77</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.png?v=45a69e38a1</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.png?v=78bf59e6bd</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.png?v=b11e893ec2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_2.png?v=462ec457c3</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.png?v=ce40d7f683</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.png?v=e1488b6f03</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.png?v=36677687b8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.png?v=770b55f1cb</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.png?v=40460a2392</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.png?v=7c32dc35c6</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.png?v=5538a2da6a</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.png?v=d8d1c20493</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.png?v=55bef0c347</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.png?v=3583dce094</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.png?v=923daa8d8d</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
